--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Dispense-Operation-Input.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Dispense-Operation-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="262">
   <si>
     <t>Property</t>
   </si>
@@ -486,6 +486,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -612,6 +622,9 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -625,24 +638,31 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
+    <t>ele-1
+inv-1</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-1
 </t>
   </si>
   <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1165,7 +1185,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="33.30859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2459,24 +2479,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2502,13 +2522,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2534,13 +2554,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2558,7 +2578,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2567,24 +2587,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2610,13 +2630,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2666,7 +2686,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2689,10 +2709,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2715,16 +2735,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2750,13 +2770,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -2774,7 +2794,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2797,10 +2817,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2823,13 +2843,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2868,7 +2888,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2878,7 +2898,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2887,24 +2907,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3007,10 +3027,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3080,16 +3100,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -3115,14 +3135,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3144,16 +3164,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3202,7 +3222,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3220,15 +3240,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3254,12 +3274,14 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3308,7 +3330,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3331,10 +3353,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3357,13 +3379,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3414,7 +3436,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3423,7 +3445,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3432,15 +3454,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3463,16 +3485,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3522,7 +3544,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3531,7 +3553,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3540,15 +3562,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3574,13 +3596,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3630,7 +3652,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3642,7 +3664,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3653,13 +3675,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3681,13 +3703,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3738,7 +3760,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3747,24 +3769,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3867,10 +3889,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3940,16 +3962,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3975,14 +3997,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4004,16 +4026,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4062,7 +4084,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4080,15 +4102,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4114,12 +4136,14 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4129,7 +4153,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4168,7 +4192,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4191,10 +4215,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4217,13 +4241,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4274,7 +4298,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4283,7 +4307,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4292,15 +4316,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4323,16 +4347,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4382,7 +4406,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4391,7 +4415,7 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>75</v>
@@ -4400,15 +4424,15 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4416,7 +4440,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>77</v>
@@ -4434,13 +4458,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4478,7 +4502,7 @@
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -4488,7 +4512,7 @@
         <v>137</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4500,7 +4524,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4511,10 +4535,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4617,10 +4641,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4690,16 +4714,16 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>111</v>
@@ -4725,14 +4749,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4754,16 +4778,16 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4812,7 +4836,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4830,15 +4854,15 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4864,12 +4888,14 @@
         <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -4918,7 +4944,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4941,10 +4967,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4967,13 +4993,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5024,7 +5050,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5033,7 +5059,7 @@
         <v>84</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -5042,15 +5068,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5073,16 +5099,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5132,7 +5158,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5141,7 +5167,7 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5150,15 +5176,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5184,13 +5210,13 @@
         <v>75</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5240,7 +5266,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5252,7 +5278,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5263,13 +5289,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5291,16 +5317,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5350,7 +5376,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5362,7 +5388,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5373,10 +5399,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5479,10 +5505,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5552,16 +5578,16 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>111</v>
@@ -5587,14 +5613,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5616,16 +5642,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5674,7 +5700,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5692,15 +5718,15 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5726,12 +5752,14 @@
         <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5741,7 +5769,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -5780,7 +5808,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5803,10 +5831,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5829,13 +5857,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5886,7 +5914,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -5895,7 +5923,7 @@
         <v>84</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5904,15 +5932,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5935,16 +5963,16 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5994,7 +6022,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6012,15 +6040,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6046,13 +6074,13 @@
         <v>75</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6102,7 +6130,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6114,7 +6142,7 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6125,13 +6153,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6153,16 +6181,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6212,7 +6240,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6224,7 +6252,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6235,10 +6263,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6341,10 +6369,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6414,16 +6442,16 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>111</v>
@@ -6449,14 +6477,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6478,16 +6506,16 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6536,7 +6564,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6554,15 +6582,15 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6588,12 +6616,14 @@
         <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -6603,7 +6633,7 @@
         <v>75</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>75</v>
@@ -6642,7 +6672,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6665,10 +6695,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6691,13 +6721,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6748,7 +6778,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -6757,7 +6787,7 @@
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6766,15 +6796,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6797,16 +6827,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6856,7 +6886,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6874,15 +6904,15 @@
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6908,13 +6938,13 @@
         <v>75</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6964,7 +6994,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -6976,7 +7006,7 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Dispense-Operation-Input.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-PAR-Dispense-Operation-Input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="256">
   <si>
     <t>Property</t>
   </si>
@@ -486,16 +486,6 @@
     <t>Meta.security</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Parameters.meta.tag</t>
   </si>
   <si>
@@ -622,9 +612,6 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -638,8 +625,8 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
-    <t>ele-1
-inv-1</t>
+    <t xml:space="preserve">inv-1
+</t>
   </si>
   <si>
     <t>Parameters.parameter.resource</t>
@@ -656,13 +643,6 @@
   </si>
   <si>
     <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -1185,7 +1165,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="48.5546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="33.30859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2479,24 +2459,24 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2522,13 +2502,13 @@
         <v>143</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2554,31 +2534,31 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2587,24 +2567,24 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>153</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2630,13 +2610,13 @@
         <v>125</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2686,7 +2666,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2709,10 +2689,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2735,16 +2715,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2770,31 +2750,31 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2817,10 +2797,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2843,13 +2823,13 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2888,7 +2868,7 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
@@ -2898,7 +2878,7 @@
         <v>137</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2907,24 +2887,24 @@
         <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3027,10 +3007,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3100,16 +3080,16 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>111</v>
@@ -3135,14 +3115,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3164,16 +3144,16 @@
         <v>104</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3222,7 +3202,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3240,15 +3220,15 @@
         <v>75</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3274,14 +3254,12 @@
         <v>98</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -3330,7 +3308,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>84</v>
@@ -3353,10 +3331,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3379,13 +3357,13 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3436,16 +3414,16 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>96</v>
@@ -3454,15 +3432,15 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3485,16 +3463,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3544,7 +3522,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3553,7 +3531,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>75</v>
@@ -3562,15 +3540,15 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3596,13 +3574,13 @@
         <v>75</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3652,7 +3630,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3664,7 +3642,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3675,13 +3653,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -3703,13 +3681,13 @@
         <v>85</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3760,7 +3738,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3769,24 +3747,24 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3889,10 +3867,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3962,16 +3940,16 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>111</v>
@@ -3997,14 +3975,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4026,16 +4004,16 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4084,7 +4062,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4102,15 +4080,15 @@
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4136,14 +4114,12 @@
         <v>98</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4153,7 +4129,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -4192,7 +4168,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>84</v>
@@ -4215,10 +4191,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4241,13 +4217,13 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4298,16 +4274,16 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>96</v>
@@ -4316,15 +4292,15 @@
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4347,16 +4323,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4406,7 +4382,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4415,7 +4391,7 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>75</v>
@@ -4424,15 +4400,15 @@
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4440,7 +4416,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>77</v>
@@ -4458,13 +4434,13 @@
         <v>75</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4502,7 +4478,7 @@
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -4512,7 +4488,7 @@
         <v>137</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4524,7 +4500,7 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
@@ -4535,10 +4511,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4641,10 +4617,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4714,16 +4690,16 @@
         <v>75</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>111</v>
@@ -4749,14 +4725,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4778,16 +4754,16 @@
         <v>104</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4836,7 +4812,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -4854,15 +4830,15 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4888,14 +4864,12 @@
         <v>98</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -4944,7 +4918,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>84</v>
@@ -4967,10 +4941,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4993,13 +4967,13 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5050,16 +5024,16 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI36" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>96</v>
@@ -5068,15 +5042,15 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5099,16 +5073,16 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5158,7 +5132,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5167,7 +5141,7 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>75</v>
@@ -5176,15 +5150,15 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>206</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5210,13 +5184,13 @@
         <v>75</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5266,7 +5240,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5278,7 +5252,7 @@
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
@@ -5289,13 +5263,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
@@ -5317,16 +5291,16 @@
         <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5376,7 +5350,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5388,7 +5362,7 @@
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5399,10 +5373,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5505,10 +5479,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5578,16 +5552,16 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>111</v>
@@ -5613,14 +5587,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5642,16 +5616,16 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5700,7 +5674,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -5718,15 +5692,15 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5752,14 +5726,12 @@
         <v>98</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5769,7 +5741,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -5808,7 +5780,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>84</v>
@@ -5831,10 +5803,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5857,13 +5829,13 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5914,16 +5886,16 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -5932,15 +5904,15 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5963,16 +5935,16 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6022,7 +5994,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6040,15 +6012,15 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6074,13 +6046,13 @@
         <v>75</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6130,7 +6102,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6142,7 +6114,7 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
@@ -6153,13 +6125,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>75</v>
@@ -6181,16 +6153,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6240,7 +6212,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6252,7 +6224,7 @@
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
@@ -6263,10 +6235,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6369,10 +6341,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6442,16 +6414,16 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>111</v>
@@ -6477,14 +6449,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6506,16 +6478,16 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6564,7 +6536,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6582,15 +6554,15 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6616,14 +6588,12 @@
         <v>98</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
@@ -6633,7 +6603,7 @@
         <v>75</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>75</v>
@@ -6672,7 +6642,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>84</v>
@@ -6695,10 +6665,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6721,13 +6691,13 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6778,16 +6748,16 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI52" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -6796,15 +6766,15 @@
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6827,16 +6797,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6886,7 +6856,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -6904,15 +6874,15 @@
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6938,13 +6908,13 @@
         <v>75</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -6994,7 +6964,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7006,7 +6976,7 @@
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
